--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104468_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104468_W2.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7308</v>
+        <v>1.3281</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9964</v>
+        <v>1.5064</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2656</v>
+        <v>-0.1783</v>
       </c>
       <c r="G2" t="n">
-        <v>0.454</v>
+        <v>0.4537</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3679</v>
+        <v>2.3694</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.9139</v>
+        <v>-1.9157</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5548</v>
+        <v>0.5346</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6451</v>
+        <v>1.6375</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.0903</v>
+        <v>-1.1029</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1008</v>
+        <v>-0.081</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7228</v>
+        <v>0.7319</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8953</v>
+        <v>0.427</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0206</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6662</v>
+        <v>0.6493</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4169</v>
+        <v>0.4229</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2493</v>
+        <v>0.2264</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0644</v>
+        <v>0.2544</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6522</v>
+        <v>-2.1942</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.7166</v>
+        <v>2.4487</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1609</v>
+        <v>0.6509</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4648</v>
+        <v>-1.4037</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3039</v>
+        <v>2.0546</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2252</v>
+        <v>-0.3965</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1874</v>
+        <v>-0.7906</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4126</v>
+        <v>0.3941</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6479</v>
+        <v>-0.2393</v>
       </c>
       <c r="T3" t="n">
-        <v>0.617</v>
+        <v>-0.1794</v>
       </c>
       <c r="U3" t="n">
-        <v>2.0309</v>
+        <v>-0.06</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.6905</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.6905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2627</v>
+        <v>0.1065</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7467</v>
+        <v>-0.7754</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0094</v>
+        <v>0.8819</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1531</v>
+        <v>-0.1475</v>
       </c>
       <c r="H4" t="n">
         <v>-0.3131</v>
       </c>
       <c r="I4" t="n">
-        <v>0.16</v>
+        <v>0.1656</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.1101</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3432</v>
+        <v>-0.3555</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.0373</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0958</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2798</v>
+        <v>0.1173</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3388</v>
+        <v>0.3363</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.059</v>
+        <v>-0.219</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5986</v>
+        <v>-0.7833</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2236</v>
+        <v>-0.0521</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.7312</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4646</v>
+        <v>-1.4612</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6939</v>
+        <v>-1.6999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2293</v>
+        <v>0.2388</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.5589</v>
+        <v>-1.579</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9218</v>
+        <v>-0.9383</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1178</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1839</v>
+        <v>0.0046</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4779</v>
+        <v>0.2388</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.294</v>
+        <v>-0.2342</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3627</v>
+        <v>1.3562</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5297</v>
+        <v>-1.5253</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7483</v>
+        <v>-1.1253</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5677</v>
+        <v>-0.3166</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1806</v>
+        <v>-0.8087</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2616</v>
+        <v>-0.0614</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1933</v>
+        <v>1.6515</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4549</v>
+        <v>-1.7129</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6896</v>
+        <v>1.1379</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.3893</v>
+        <v>1.4511</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0789</v>
+        <v>-0.3132</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.428</v>
+        <v>-1.1993</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8038999999999999</v>
+        <v>0.2003</v>
       </c>
       <c r="O6" t="n">
-        <v>0.376</v>
+        <v>-1.3997</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6489</v>
+        <v>0.8468</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2158</v>
+        <v>-0.0887</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4331</v>
+        <v>0.9355</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>-1.683</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.683</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.031</v>
+        <v>-1.4214</v>
       </c>
       <c r="E7" t="n">
+        <v>0.5073</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.9287</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6573</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.1696</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8269</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0545</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.6028</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.1868</v>
+      </c>
+      <c r="O7" t="n">
         <v>0.7896</v>
       </c>
-      <c r="F7" t="n">
-        <v>-1.8206</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.6519</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.1717</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.8237</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.0546</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.0173</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.0373</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.5973000000000001</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-0.1891</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.7864</v>
-      </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>0.597</v>
+        <v>0.1881</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7349</v>
+        <v>0.4528</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1379</v>
+        <v>-0.2647</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.5068</v>
+        <v>-2.4945</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.5068</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="8">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5586</v>
+        <v>-1.4955</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9527</v>
+        <v>-0.9567</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.606</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3221</v>
+        <v>-1.3213</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4794</v>
+        <v>-1.4792</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2365</v>
+        <v>-0.1743</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3401</v>
+        <v>-1.7049</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8646</v>
+        <v>-0.4109</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4756</v>
+        <v>-1.294</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4281</v>
+        <v>0.4325</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2495</v>
+        <v>0.2553</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1786</v>
+        <v>0.1772</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1043</v>
+        <v>1.0899</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6762</v>
+        <v>-0.6574</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5580000000000001</v>
+        <v>0.0708</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6079</v>
+        <v>-0.135</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0499</v>
+        <v>0.2058</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5297</v>
+        <v>-1.5253</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5297</v>
+        <v>-1.5253</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9458</v>
+        <v>-2.1358</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2502</v>
+        <v>-2.7459</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3044</v>
+        <v>0.6101</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3599</v>
+        <v>-2.359</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5873</v>
+        <v>-0.5833</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7726</v>
+        <v>-1.7758</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.4301</v>
+        <v>-2.4463</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1456</v>
+        <v>-0.1519</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0701</v>
+        <v>0.0873</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7709</v>
+        <v>0.0523</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4688</v>
+        <v>0.0741</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3021</v>
+        <v>-0.0218</v>
       </c>
       <c r="V10" t="n">
-        <v>2.6802</v>
+        <v>2.6749</v>
       </c>
       <c r="W10" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5978</v>
+        <v>-0.5936</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1326</v>
+        <v>-2.9928</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4021</v>
+        <v>-1.4136</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7305</v>
+        <v>-1.5792</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0471</v>
+        <v>-2.053</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8585</v>
+        <v>0.8642</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.9055</v>
+        <v>-2.9172</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9977</v>
+        <v>-1.0232</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1429</v>
+        <v>1.1376</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.1406</v>
+        <v>-2.1608</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0494</v>
+        <v>-1.0298</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1948</v>
+        <v>-0.0487</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0907</v>
+        <v>0.1136</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2855</v>
+        <v>-0.1623</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4371</v>
+        <v>-0.4358</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5297</v>
+        <v>-1.5253</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.108</v>
+        <v>-5.2745</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8544</v>
+        <v>-4.0104</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2537</v>
+        <v>-1.2642</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2528</v>
+        <v>-1.2523</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0316</v>
+        <v>-1.0366</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2212</v>
+        <v>-0.2158</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1389</v>
+        <v>-1.1541</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4644</v>
+        <v>-0.4761</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.114</v>
+        <v>-0.0982</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7891</v>
+        <v>0.0476</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8347</v>
+        <v>0.0346</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0457</v>
+        <v>0.013</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.0114</v>
+        <v>-7.2289</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.166</v>
+        <v>-5.6944</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8454</v>
+        <v>-1.5345</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.5267</v>
+        <v>-3.5378</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7328</v>
+        <v>-1.7428</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7939</v>
+        <v>-1.795</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.3624</v>
+        <v>-3.3991</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4484</v>
+        <v>-1.4694</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.914</v>
+        <v>-1.9298</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1644</v>
+        <v>-0.1387</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1201</v>
+        <v>0.1347</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.031</v>
+        <v>-0.2358</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3085</v>
+        <v>0.2086</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7226</v>
+        <v>-0.4444</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-23.8147</v>
+        <v>-22.0785</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.3779</v>
+        <v>-13.9394</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.437000000000001</v>
+        <v>-8.139199999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.3951</v>
+        <v>-10.3956</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.438299999999999</v>
+        <v>-2.441199999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.956599999999999</v>
+        <v>-7.9544</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.685599999999999</v>
+        <v>-6.9219</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4059000000000008</v>
+        <v>0.2930999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-7.0913</v>
+        <v>-7.2153</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.7097</v>
+        <v>-3.4736</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.8442</v>
+        <v>-2.7345</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8652000000000003</v>
+        <v>-0.7390999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.805200000000001</v>
+        <v>-6.829099999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-15.8783</v>
+        <v>-15.9341</v>
       </c>
       <c r="R14" t="n">
-        <v>9.073399999999999</v>
+        <v>9.105400000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6048000000000001</v>
+        <v>1.138</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5593000000000002</v>
+        <v>1.2039</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0454</v>
+        <v>-0.06589999999999996</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.0096</v>
+        <v>-5.991999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>7.7453</v>
+        <v>7.712599999999998</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.7549</v>
+        <v>-13.7049</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9037</v>
+        <v>6.265</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9042</v>
+        <v>3.3765</v>
       </c>
       <c r="F15" t="n">
-        <v>3.9995</v>
+        <v>2.8885</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3499</v>
+        <v>4.5203</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5453</v>
+        <v>1.5131</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8953</v>
+        <v>3.0072</v>
       </c>
       <c r="J15" t="n">
-        <v>0.168</v>
+        <v>2.1062</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0559</v>
+        <v>0.9825</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2239</v>
+        <v>1.1237</v>
       </c>
       <c r="M15" t="n">
-        <v>1.182</v>
+        <v>2.4142</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4894</v>
+        <v>0.5306</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6714</v>
+        <v>1.8835</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3004</v>
+        <v>0.6959</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5243</v>
+        <v>0.1808</v>
       </c>
       <c r="U15" t="n">
-        <v>0.776</v>
+        <v>0.5151</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3461</v>
+        <v>-0.5447</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3461</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3115</v>
+        <v>6.0101</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4605</v>
+        <v>2.1674</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8509</v>
+        <v>3.8428</v>
       </c>
       <c r="G16" t="n">
-        <v>4.5195</v>
+        <v>1.353</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5049</v>
+        <v>-0.5511</v>
       </c>
       <c r="I16" t="n">
-        <v>3.0147</v>
+        <v>1.9041</v>
       </c>
       <c r="J16" t="n">
-        <v>2.133</v>
+        <v>0.147</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9871</v>
+        <v>-0.0764</v>
       </c>
       <c r="L16" t="n">
-        <v>1.146</v>
+        <v>0.2234</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3865</v>
+        <v>1.206</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5178</v>
+        <v>-0.4747</v>
       </c>
       <c r="O16" t="n">
-        <v>1.8687</v>
+        <v>1.6807</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2495</v>
+        <v>1.4099</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7652</v>
+        <v>0.8218</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.5881</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>2.3367</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>2.3367</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.6251</v>
+        <v>3.6202</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0636</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5615</v>
+        <v>2.7398</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1883</v>
+        <v>2.1937</v>
       </c>
       <c r="H17" t="n">
-        <v>1.29</v>
+        <v>1.2923</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8983</v>
+        <v>0.9014</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1914</v>
+        <v>0.1839</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8658</v>
+        <v>0.8618</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9968</v>
+        <v>2.0097</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4241</v>
+        <v>0.4305</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5727</v>
+        <v>1.5793</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>1.851</v>
+        <v>0.8316</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8721</v>
+        <v>0.6965</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0212</v>
+        <v>0.135</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5311</v>
+        <v>2.8801</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0822</v>
+        <v>1.4794</v>
       </c>
       <c r="F18" t="n">
-        <v>1.449</v>
+        <v>1.4007</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3998</v>
+        <v>3.4153</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3333</v>
+        <v>1.1861</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0665</v>
+        <v>2.2292</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5548999999999999</v>
+        <v>1.1578</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7415</v>
+        <v>0.1239</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1866</v>
+        <v>1.0339</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1551</v>
+        <v>2.2575</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4082</v>
+        <v>1.0622</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2531</v>
+        <v>1.1953</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0897</v>
+        <v>0.0582</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3157</v>
+        <v>-0.1258</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2259</v>
+        <v>0.184</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7071</v>
+        <v>0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3214</v>
+        <v>2.7237</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3856</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3529</v>
+        <v>2.8569</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5218</v>
+        <v>1.7353</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8310999999999999</v>
+        <v>1.1216</v>
       </c>
       <c r="G19" t="n">
-        <v>2.2654</v>
+        <v>2.2737</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9855</v>
+        <v>1.9874</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2799</v>
+        <v>0.2863</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6116</v>
+        <v>1.5939</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7663</v>
+        <v>1.7582</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1547</v>
+        <v>-0.1643</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6538</v>
+        <v>0.6798</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4346</v>
+        <v>0.4506</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3408</v>
+        <v>0.8305</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0484</v>
+        <v>0.1901</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3892</v>
+        <v>0.6404</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8178</v>
+        <v>2.0665</v>
       </c>
       <c r="E20" t="n">
-        <v>0.826</v>
+        <v>1.5361</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9918</v>
+        <v>0.5304</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4315</v>
+        <v>-0.7034</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1846</v>
+        <v>-0.6662</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2469</v>
+        <v>-0.0372</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1974</v>
+        <v>0.3552</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1314</v>
+        <v>0.1099</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0659</v>
+        <v>0.2453</v>
       </c>
       <c r="M20" t="n">
-        <v>2.2342</v>
+        <v>-1.0587</v>
       </c>
       <c r="N20" t="n">
-        <v>1.0532</v>
+        <v>-0.7761</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1809</v>
+        <v>-0.2826</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0259</v>
+        <v>-0.4577</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8347</v>
+        <v>-0.4533</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1912</v>
+        <v>-0.0044</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5463</v>
+        <v>1.6342</v>
       </c>
       <c r="W20" t="n">
-        <v>2.7317</v>
+        <v>1.6342</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2966</v>
+        <v>1.634</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1866</v>
+        <v>0.4165</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1101</v>
+        <v>1.2175</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9558</v>
+        <v>0.9614</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3347</v>
+        <v>0.3387</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6211</v>
+        <v>0.6227</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5344</v>
+        <v>0.5281</v>
       </c>
       <c r="K21" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4824</v>
+        <v>0.4764</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4214</v>
+        <v>0.4333</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3396</v>
+        <v>-0.0104</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3478</v>
+        <v>-0.1116</v>
       </c>
       <c r="U21" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.1013</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0717</v>
+        <v>1.3476</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9757</v>
+        <v>-0.3482</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0959</v>
+        <v>1.6958</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.701</v>
+        <v>-0.3874</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6637</v>
+        <v>-0.3359</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0373</v>
+        <v>-0.0515</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3801</v>
+        <v>-0.5657</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1243</v>
+        <v>-0.7519</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2558</v>
+        <v>0.1862</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0812</v>
+        <v>0.1784</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.788</v>
+        <v>0.416</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2931</v>
+        <v>-0.2377</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4541</v>
+        <v>-0.1057</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0434</v>
+        <v>-0.098</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4107</v>
+        <v>-0.0077</v>
       </c>
       <c r="V22" t="n">
-        <v>1.639</v>
+        <v>0.7025</v>
       </c>
       <c r="W22" t="n">
-        <v>1.639</v>
+        <v>0.3155</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6832</v>
+        <v>0.7221</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5375</v>
+        <v>-0.4654</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2206</v>
+        <v>1.1875</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4043</v>
+        <v>-1.4287</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7645</v>
+        <v>-0.7803</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6398</v>
+        <v>-0.6484</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.35</v>
+        <v>-0.3977</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3699</v>
+        <v>0.3405</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7198</v>
+        <v>-0.7382</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0543</v>
+        <v>-1.031</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O23" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>0.046</v>
+        <v>0.1021</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1875</v>
+        <v>-0.0678</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2335</v>
+        <v>0.1699</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>D. ENNIS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.2032</v>
+        <v>-0.7179</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6558</v>
+        <v>-1.8459</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5473</v>
+        <v>1.128</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8935</v>
+        <v>-2.7052</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1312</v>
+        <v>-1.6832</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7623</v>
+        <v>-1.022</v>
       </c>
       <c r="J24" t="n">
-        <v>0.477</v>
+        <v>-2.1059</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0693</v>
+        <v>-0.7347</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4078</v>
+        <v>-1.3712</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4165</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0619</v>
+        <v>-0.9485</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3546</v>
+        <v>0.3492</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2574</v>
+        <v>-0.8258</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1179</v>
+        <v>-0.7321</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1394</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9320000000000001</v>
+        <v>3.2684</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2534</v>
+        <v>3.2684</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. ENNIS</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.5757</v>
+        <v>-1.2843</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3904</v>
+        <v>-0.7931</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8147</v>
+        <v>-0.4911</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.7037</v>
+        <v>0.9029</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6854</v>
+        <v>0.1402</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0183</v>
+        <v>0.7627</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.0784</v>
+        <v>0.4709</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7242</v>
+        <v>0.0689</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3542</v>
+        <v>0.4019</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.6252</v>
+        <v>0.432</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9612000000000001</v>
+        <v>0.0713</v>
       </c>
       <c r="O25" t="n">
-        <v>0.336</v>
+        <v>0.3608</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6964</v>
+        <v>-0.345</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3217</v>
+        <v>-0.2349</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3747</v>
+        <v>-0.11</v>
       </c>
       <c r="V25" t="n">
-        <v>3.278</v>
+        <v>-0.9317</v>
       </c>
       <c r="W25" t="n">
-        <v>3.278</v>
+        <v>1.2472</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>23.8147</v>
+        <v>25.4003</v>
       </c>
       <c r="E26" t="n">
-        <v>8.436900000000001</v>
+        <v>8.139099999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>15.3778</v>
+        <v>17.2615</v>
       </c>
       <c r="G26" t="n">
-        <v>10.3951</v>
+        <v>10.3956</v>
       </c>
       <c r="H26" t="n">
-        <v>2.4387</v>
+        <v>2.4411</v>
       </c>
       <c r="I26" t="n">
-        <v>7.956600000000002</v>
+        <v>7.954499999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>3.709600000000001</v>
+        <v>3.473699999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>2.8445</v>
+        <v>2.7344</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8653</v>
+        <v>0.7391999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>6.685599999999999</v>
+        <v>6.921899999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4058000000000003</v>
+        <v>-0.2934000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>7.0914</v>
+        <v>7.2152</v>
       </c>
       <c r="P26" t="n">
-        <v>6.8049</v>
+        <v>6.828899999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-9.0733</v>
+        <v>-9.1053</v>
       </c>
       <c r="R26" t="n">
-        <v>15.8783</v>
+        <v>15.9343</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6050000000000002</v>
+        <v>2.1836</v>
       </c>
       <c r="T26" t="n">
-        <v>0.04549999999999987</v>
+        <v>0.06569999999999976</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5593999999999997</v>
+        <v>2.118</v>
       </c>
       <c r="V26" t="n">
-        <v>6.0097</v>
+        <v>5.9921</v>
       </c>
       <c r="W26" t="n">
-        <v>13.755</v>
+        <v>13.7047</v>
       </c>
       <c r="X26" t="n">
-        <v>-7.7451</v>
+        <v>-7.7125</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104468_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104468_W2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.5253</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.683</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.5253</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5936</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.5253</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-13.7049</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104468_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-7.7125</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
